--- a/informe 2/datos2.xlsx
+++ b/informe 2/datos2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srome\OneDrive\Documentos\Universidad\Digital\informes lab\liga-del-autismo-v\informe 2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66778DA6-10D6-4A56-8AF4-E34A344468C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,28 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +56,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -45,12 +64,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +385,2622 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C237"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C1" s="1">
+        <v>22.97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>507</v>
+      </c>
+      <c r="B2" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C2" s="2">
+        <v>22.87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B3" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C3" s="2">
+        <v>23.07</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>1510</v>
+      </c>
+      <c r="B4" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C4" s="2">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B5" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C5" s="2">
+        <v>25.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>2513</v>
+      </c>
+      <c r="B6" s="2">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="C6" s="2">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>3015</v>
+      </c>
+      <c r="B7" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C7" s="2">
+        <v>25.02</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>3516</v>
+      </c>
+      <c r="B8" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C8" s="2">
+        <v>24.93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>4018</v>
+      </c>
+      <c r="B9" s="2">
+        <v>20.53</v>
+      </c>
+      <c r="C9" s="2">
+        <v>24.54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>4519</v>
+      </c>
+      <c r="B10" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C10" s="2">
+        <v>25.61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>5021</v>
+      </c>
+      <c r="B11" s="2">
+        <v>21.02</v>
+      </c>
+      <c r="C11" s="2">
+        <v>21.51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>5522</v>
+      </c>
+      <c r="B12" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C12" s="2">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>6024</v>
+      </c>
+      <c r="B13" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C13" s="2">
+        <v>26.39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>6525</v>
+      </c>
+      <c r="B14" s="2">
+        <v>21.02</v>
+      </c>
+      <c r="C14" s="2">
+        <v>26.69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>7027</v>
+      </c>
+      <c r="B15" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C15" s="2">
+        <v>26.88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>7528</v>
+      </c>
+      <c r="B16" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C16" s="2">
+        <v>26.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>8030</v>
+      </c>
+      <c r="B17" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C17" s="2">
+        <v>27.47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>8531</v>
+      </c>
+      <c r="B18" s="2">
+        <v>21.02</v>
+      </c>
+      <c r="C18" s="2">
+        <v>27.17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>9033</v>
+      </c>
+      <c r="B19" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C19" s="2">
+        <v>27.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>9535</v>
+      </c>
+      <c r="B20" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C20" s="2">
+        <v>27.57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>10036</v>
+      </c>
+      <c r="B21" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C21" s="2">
+        <v>27.57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>10537</v>
+      </c>
+      <c r="B22" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C22" s="2">
+        <v>27.96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>11039</v>
+      </c>
+      <c r="B23" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C23" s="2">
+        <v>27.76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>11541</v>
+      </c>
+      <c r="B24" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C24" s="2">
+        <v>27.76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>12043</v>
+      </c>
+      <c r="B25" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C25" s="2">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>12544</v>
+      </c>
+      <c r="B26" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C26" s="2">
+        <v>27.86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>13045</v>
+      </c>
+      <c r="B27" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C27" s="2">
+        <v>26.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>13547</v>
+      </c>
+      <c r="B28" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C28" s="2">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="2">
+        <v>14049</v>
+      </c>
+      <c r="B29" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C29" s="2">
+        <v>28.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
+        <v>14551</v>
+      </c>
+      <c r="B30" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C30" s="2">
+        <v>28.35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
+        <v>15051</v>
+      </c>
+      <c r="B31" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C31" s="2">
+        <v>28.54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>15553</v>
+      </c>
+      <c r="B32" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C32" s="2">
+        <v>25.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>16055</v>
+      </c>
+      <c r="B33" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C33" s="2">
+        <v>28.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="2">
+        <v>16557</v>
+      </c>
+      <c r="B34" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C34" s="2">
+        <v>28.54</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="2">
+        <v>17058</v>
+      </c>
+      <c r="B35" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C35" s="2">
+        <v>28.74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="2">
+        <v>17559</v>
+      </c>
+      <c r="B36" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C36" s="2">
+        <v>27.76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="2">
+        <v>18061</v>
+      </c>
+      <c r="B37" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C37" s="2">
+        <v>27.76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="2">
+        <v>18563</v>
+      </c>
+      <c r="B38" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C38" s="2">
+        <v>29.72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="2">
+        <v>19064</v>
+      </c>
+      <c r="B39" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C39" s="2">
+        <v>28.84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="2">
+        <v>19566</v>
+      </c>
+      <c r="B40" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C40" s="2">
+        <v>28.93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="2">
+        <v>20067</v>
+      </c>
+      <c r="B41" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C41" s="2">
+        <v>28.84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="2">
+        <v>20569</v>
+      </c>
+      <c r="B42" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C42" s="2">
+        <v>27.57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="2">
+        <v>21070</v>
+      </c>
+      <c r="B43" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C43" s="2">
+        <v>28.93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="2">
+        <v>21572</v>
+      </c>
+      <c r="B44" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C44" s="2">
+        <v>28.93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="2">
+        <v>22074</v>
+      </c>
+      <c r="B45" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C45" s="2">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="2">
+        <v>22575</v>
+      </c>
+      <c r="B46" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C46" s="2">
+        <v>27.27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="2">
+        <v>23076</v>
+      </c>
+      <c r="B47" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C47" s="2">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="2">
+        <v>23578</v>
+      </c>
+      <c r="B48" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C48" s="2">
+        <v>29.23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="2">
+        <v>24080</v>
+      </c>
+      <c r="B49" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C49" s="2">
+        <v>29.23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="2">
+        <v>24582</v>
+      </c>
+      <c r="B50" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C50" s="2">
+        <v>29.23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="2">
+        <v>25082</v>
+      </c>
+      <c r="B51" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C51" s="2">
+        <v>31.38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="2">
+        <v>25584</v>
+      </c>
+      <c r="B52" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C52" s="2">
+        <v>26.59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="2">
+        <v>26086</v>
+      </c>
+      <c r="B53" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C53" s="2">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="2">
+        <v>26588</v>
+      </c>
+      <c r="B54" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C54" s="2">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="2">
+        <v>27089</v>
+      </c>
+      <c r="B55" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C55" s="2">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="2">
+        <v>27591</v>
+      </c>
+      <c r="B56" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C56" s="2">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="2">
+        <v>28092</v>
+      </c>
+      <c r="B57" s="2">
+        <v>21.02</v>
+      </c>
+      <c r="C57" s="2">
+        <v>27.76</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="2">
+        <v>28594</v>
+      </c>
+      <c r="B58" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C58" s="2">
+        <v>29.33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="2">
+        <v>29095</v>
+      </c>
+      <c r="B59" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C59" s="2">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="2">
+        <v>29597</v>
+      </c>
+      <c r="B60" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C60" s="2">
+        <v>29.52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="2">
+        <v>30099</v>
+      </c>
+      <c r="B61" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C61" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="2">
+        <v>30600</v>
+      </c>
+      <c r="B62" s="2">
+        <v>26.39</v>
+      </c>
+      <c r="C62" s="2">
+        <v>29.23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="2">
+        <v>31101</v>
+      </c>
+      <c r="B63" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C63" s="2">
+        <v>26.78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="2">
+        <v>31603</v>
+      </c>
+      <c r="B64" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C64" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="2">
+        <v>32105</v>
+      </c>
+      <c r="B65" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C65" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="2">
+        <v>32607</v>
+      </c>
+      <c r="B66" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C66" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="2">
+        <v>33107</v>
+      </c>
+      <c r="B67" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C67" s="2">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="2">
+        <v>33609</v>
+      </c>
+      <c r="B68" s="2">
+        <v>20.53</v>
+      </c>
+      <c r="C68" s="2">
+        <v>29.52</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="2">
+        <v>34111</v>
+      </c>
+      <c r="B69" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C69" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="2">
+        <v>34613</v>
+      </c>
+      <c r="B70" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C70" s="2">
+        <v>29.72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="2">
+        <v>35115</v>
+      </c>
+      <c r="B71" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C71" s="2">
+        <v>29.23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="2">
+        <v>35615</v>
+      </c>
+      <c r="B72" s="2">
+        <v>26.39</v>
+      </c>
+      <c r="C72" s="2">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="2">
+        <v>36117</v>
+      </c>
+      <c r="B73" s="2">
+        <v>20.04</v>
+      </c>
+      <c r="C73" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="2">
+        <v>36619</v>
+      </c>
+      <c r="B74" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C74" s="2">
+        <v>29.81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="2">
+        <v>37121</v>
+      </c>
+      <c r="B75" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C75" s="2">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="2">
+        <v>37622</v>
+      </c>
+      <c r="B76" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C76" s="2">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="2">
+        <v>38124</v>
+      </c>
+      <c r="B77" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C77" s="2">
+        <v>28.05</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="2">
+        <v>38625</v>
+      </c>
+      <c r="B78" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C78" s="2">
+        <v>29.52</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="2">
+        <v>39127</v>
+      </c>
+      <c r="B79" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C79" s="2">
+        <v>28.54</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="2">
+        <v>39628</v>
+      </c>
+      <c r="B80" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C80" s="2">
+        <v>29.81</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="2">
+        <v>40130</v>
+      </c>
+      <c r="B81" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C81" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="2">
+        <v>40632</v>
+      </c>
+      <c r="B82" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C82" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="2">
+        <v>41133</v>
+      </c>
+      <c r="B83" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C83" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="2">
+        <v>41634</v>
+      </c>
+      <c r="B84" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C84" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="2">
+        <v>42136</v>
+      </c>
+      <c r="B85" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C85" s="2">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="2">
+        <v>42638</v>
+      </c>
+      <c r="B86" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C86" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="2">
+        <v>43140</v>
+      </c>
+      <c r="B87" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C87" s="2">
+        <v>29.81</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="2">
+        <v>43640</v>
+      </c>
+      <c r="B88" s="2">
+        <v>26.88</v>
+      </c>
+      <c r="C88" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="2">
+        <v>44142</v>
+      </c>
+      <c r="B89" s="2">
+        <v>27.37</v>
+      </c>
+      <c r="C89" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A90" s="2">
+        <v>44644</v>
+      </c>
+      <c r="B90" s="2">
+        <v>26.39</v>
+      </c>
+      <c r="C90" s="2">
+        <v>30.69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="2">
+        <v>45146</v>
+      </c>
+      <c r="B91" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C91" s="2">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="2">
+        <v>45647</v>
+      </c>
+      <c r="B92" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C92" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B93" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C93" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="2">
+        <v>46650</v>
+      </c>
+      <c r="B94" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C94" s="2">
+        <v>31.87</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A95" s="2">
+        <v>47152</v>
+      </c>
+      <c r="B95" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C95" s="2">
+        <v>28.74</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="2">
+        <v>47653</v>
+      </c>
+      <c r="B96" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C96" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="2">
+        <v>48155</v>
+      </c>
+      <c r="B97" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C97" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="2">
+        <v>48656</v>
+      </c>
+      <c r="B98" s="2">
+        <v>26.39</v>
+      </c>
+      <c r="C98" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="2">
+        <v>49158</v>
+      </c>
+      <c r="B99" s="2">
+        <v>26.39</v>
+      </c>
+      <c r="C99" s="2">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="2">
+        <v>49659</v>
+      </c>
+      <c r="B100" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C100" s="2">
+        <v>28.64</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="2">
+        <v>50161</v>
+      </c>
+      <c r="B101" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C101" s="2">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="2">
+        <v>50663</v>
+      </c>
+      <c r="B102" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C102" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="2">
+        <v>51165</v>
+      </c>
+      <c r="B103" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C103" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="2">
+        <v>51665</v>
+      </c>
+      <c r="B104" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C104" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="2">
+        <v>52167</v>
+      </c>
+      <c r="B105" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C105" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="2">
+        <v>52669</v>
+      </c>
+      <c r="B106" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C106" s="2">
+        <v>29.81</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="2">
+        <v>53171</v>
+      </c>
+      <c r="B107" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C107" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A108" s="2">
+        <v>53672</v>
+      </c>
+      <c r="B108" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C108" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A109" s="2">
+        <v>54173</v>
+      </c>
+      <c r="B109" s="2">
+        <v>27.37</v>
+      </c>
+      <c r="C109" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="2">
+        <v>54675</v>
+      </c>
+      <c r="B110" s="2">
+        <v>26.88</v>
+      </c>
+      <c r="C110" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A111" s="2">
+        <v>55177</v>
+      </c>
+      <c r="B111" s="2">
+        <v>27.37</v>
+      </c>
+      <c r="C111" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A112" s="2">
+        <v>55678</v>
+      </c>
+      <c r="B112" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C112" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A113" s="2">
+        <v>56180</v>
+      </c>
+      <c r="B113" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C113" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A114" s="2">
+        <v>56681</v>
+      </c>
+      <c r="B114" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C114" s="2">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A115" s="2">
+        <v>57183</v>
+      </c>
+      <c r="B115" s="2">
+        <v>26.88</v>
+      </c>
+      <c r="C115" s="2">
+        <v>30.11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A116" s="2">
+        <v>57684</v>
+      </c>
+      <c r="B116" s="2">
+        <v>20.53</v>
+      </c>
+      <c r="C116" s="2">
+        <v>29.03</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="2">
+        <v>58186</v>
+      </c>
+      <c r="B117" s="2">
+        <v>26.39</v>
+      </c>
+      <c r="C117" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A118" s="2">
+        <v>58688</v>
+      </c>
+      <c r="B118" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C118" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A119" s="2">
+        <v>59189</v>
+      </c>
+      <c r="B119" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C119" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A120" s="2">
+        <v>59691</v>
+      </c>
+      <c r="B120" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C120" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A121" s="2">
+        <v>60192</v>
+      </c>
+      <c r="B121" s="2">
+        <v>27.37</v>
+      </c>
+      <c r="C121" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A122" s="2">
+        <v>60694</v>
+      </c>
+      <c r="B122" s="2">
+        <v>26.39</v>
+      </c>
+      <c r="C122" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A123" s="2">
+        <v>61196</v>
+      </c>
+      <c r="B123" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C123" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="2">
+        <v>61698</v>
+      </c>
+      <c r="B124" s="2">
+        <v>25.42</v>
+      </c>
+      <c r="C124" s="2">
+        <v>30.21</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A125" s="2">
+        <v>62198</v>
+      </c>
+      <c r="B125" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C125" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A126" s="2">
+        <v>62700</v>
+      </c>
+      <c r="B126" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C126" s="2">
+        <v>28.15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="2">
+        <v>63202</v>
+      </c>
+      <c r="B127" s="2">
+        <v>24.93</v>
+      </c>
+      <c r="C127" s="2">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="2">
+        <v>63704</v>
+      </c>
+      <c r="B128" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C128" s="2">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="2">
+        <v>64205</v>
+      </c>
+      <c r="B129" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="C129" s="2">
+        <v>29.52</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A130" s="2">
+        <v>64706</v>
+      </c>
+      <c r="B130" s="2">
+        <v>27.86</v>
+      </c>
+      <c r="C130" s="2">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A131" s="2">
+        <v>65208</v>
+      </c>
+      <c r="B131" s="2">
+        <v>24.44</v>
+      </c>
+      <c r="C131" s="2">
+        <v>29.23</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A132" s="2">
+        <v>65710</v>
+      </c>
+      <c r="B132" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C132" s="2">
+        <v>29.91</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A133" s="2">
+        <v>66211</v>
+      </c>
+      <c r="B133" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C133" s="2">
+        <v>29.62</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A134" s="2">
+        <v>66713</v>
+      </c>
+      <c r="B134" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C134" s="2">
+        <v>29.52</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A135" s="2">
+        <v>67214</v>
+      </c>
+      <c r="B135" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C135" s="2">
+        <v>29.52</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A136" s="2">
+        <v>67716</v>
+      </c>
+      <c r="B136" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C136" s="2">
+        <v>29.42</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="2">
+        <v>68217</v>
+      </c>
+      <c r="B137" s="2">
+        <v>23.46</v>
+      </c>
+      <c r="C137" s="2">
+        <v>28.54</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A138" s="2">
+        <v>68719</v>
+      </c>
+      <c r="B138" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C138" s="2">
+        <v>28.74</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A139" s="2">
+        <v>69221</v>
+      </c>
+      <c r="B139" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C139" s="2">
+        <v>28.35</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A140" s="2">
+        <v>69722</v>
+      </c>
+      <c r="B140" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C140" s="2">
+        <v>28.35</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="2">
+        <v>70223</v>
+      </c>
+      <c r="B141" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C141" s="2">
+        <v>27.86</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A142" s="2">
+        <v>70725</v>
+      </c>
+      <c r="B142" s="2">
+        <v>23.95</v>
+      </c>
+      <c r="C142" s="2">
+        <v>28.15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A143" s="2">
+        <v>71227</v>
+      </c>
+      <c r="B143" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C143" s="2">
+        <v>25.51</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A144" s="2">
+        <v>71729</v>
+      </c>
+      <c r="B144" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C144" s="2">
+        <v>27.27</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A145" s="2">
+        <v>72229</v>
+      </c>
+      <c r="B145" s="2">
+        <v>22.97</v>
+      </c>
+      <c r="C145" s="2">
+        <v>27.08</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A146" s="2">
+        <v>72731</v>
+      </c>
+      <c r="B146" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C146" s="2">
+        <v>26.78</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A147" s="2">
+        <v>73233</v>
+      </c>
+      <c r="B147" s="2">
+        <v>20.04</v>
+      </c>
+      <c r="C147" s="2">
+        <v>26.39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A148" s="2">
+        <v>73735</v>
+      </c>
+      <c r="B148" s="2">
+        <v>22.48</v>
+      </c>
+      <c r="C148" s="2">
+        <v>26.49</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A149" s="2">
+        <v>74236</v>
+      </c>
+      <c r="B149" s="2">
+        <v>20.04</v>
+      </c>
+      <c r="C149" s="2">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A150" s="2">
+        <v>74738</v>
+      </c>
+      <c r="B150" s="2">
+        <v>21.02</v>
+      </c>
+      <c r="C150" s="2">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="2">
+        <v>75239</v>
+      </c>
+      <c r="B151" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C151" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="2">
+        <v>75741</v>
+      </c>
+      <c r="B152" s="2">
+        <v>21.99</v>
+      </c>
+      <c r="C152" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A153" s="2">
+        <v>76242</v>
+      </c>
+      <c r="B153" s="2">
+        <v>21.51</v>
+      </c>
+      <c r="C153" s="2">
+        <v>25.61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A154" s="2">
+        <v>76744</v>
+      </c>
+      <c r="B154" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C154" s="2">
+        <v>25.71</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A155" s="2">
+        <v>77246</v>
+      </c>
+      <c r="B155" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C155" s="2">
+        <v>25.32</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A156" s="2">
+        <v>77747</v>
+      </c>
+      <c r="B156" s="2">
+        <v>21.02</v>
+      </c>
+      <c r="C156" s="2">
+        <v>25.42</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A157" s="2">
+        <v>78248</v>
+      </c>
+      <c r="B157" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C157" s="2">
+        <v>25.22</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="2">
+        <v>78750</v>
+      </c>
+      <c r="B158" s="2">
+        <v>20.04</v>
+      </c>
+      <c r="C158" s="2">
+        <v>25.12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A159" s="2">
+        <v>79252</v>
+      </c>
+      <c r="B159" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C159" s="2">
+        <v>25.32</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="2">
+        <v>79754</v>
+      </c>
+      <c r="B160" s="2">
+        <v>20.04</v>
+      </c>
+      <c r="C160" s="2">
+        <v>25.61</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A161" s="2">
+        <v>80254</v>
+      </c>
+      <c r="B161" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C161" s="2">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A162" s="2">
+        <v>80756</v>
+      </c>
+      <c r="B162" s="2">
+        <v>20.53</v>
+      </c>
+      <c r="C162" s="2">
+        <v>24.63</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A163" s="2">
+        <v>81258</v>
+      </c>
+      <c r="B163" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C163" s="2">
+        <v>24.63</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A164" s="2">
+        <v>81760</v>
+      </c>
+      <c r="B164" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C164" s="2">
+        <v>24.63</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A165" s="2">
+        <v>82262</v>
+      </c>
+      <c r="B165" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C165" s="2">
+        <v>24.44</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A166" s="2">
+        <v>82762</v>
+      </c>
+      <c r="B166" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C166" s="2">
+        <v>22.97</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A167" s="2">
+        <v>83264</v>
+      </c>
+      <c r="B167" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C167" s="2">
+        <v>24.24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A168" s="2">
+        <v>83766</v>
+      </c>
+      <c r="B168" s="2">
+        <v>20.53</v>
+      </c>
+      <c r="C168" s="2">
+        <v>24.24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A169" s="2">
+        <v>84268</v>
+      </c>
+      <c r="B169" s="2">
+        <v>20.04</v>
+      </c>
+      <c r="C169" s="2">
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A170" s="2">
+        <v>84769</v>
+      </c>
+      <c r="B170" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C170" s="2">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A171" s="2">
+        <v>85270</v>
+      </c>
+      <c r="B171" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C171" s="2">
+        <v>24.83</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A172" s="2">
+        <v>85772</v>
+      </c>
+      <c r="B172" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C172" s="2">
+        <v>23.85</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A173" s="2">
+        <v>86274</v>
+      </c>
+      <c r="B173" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C173" s="2">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A174" s="2">
+        <v>86775</v>
+      </c>
+      <c r="B174" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C174" s="2">
+        <v>23.56</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A175" s="2">
+        <v>87277</v>
+      </c>
+      <c r="B175" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C175" s="2">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="2">
+        <v>87778</v>
+      </c>
+      <c r="B176" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C176" s="2">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A177" s="2">
+        <v>88280</v>
+      </c>
+      <c r="B177" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C177" s="2">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A178" s="2">
+        <v>88781</v>
+      </c>
+      <c r="B178" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C178" s="2">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A179" s="2">
+        <v>89283</v>
+      </c>
+      <c r="B179" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C179" s="2">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A180" s="2">
+        <v>89785</v>
+      </c>
+      <c r="B180" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C180" s="2">
+        <v>25.12</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A181" s="2">
+        <v>90286</v>
+      </c>
+      <c r="B181" s="2">
+        <v>19.55</v>
+      </c>
+      <c r="C181" s="2">
+        <v>23.36</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A182" s="2">
+        <v>90787</v>
+      </c>
+      <c r="B182" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C182" s="2">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A183" s="2">
+        <v>91289</v>
+      </c>
+      <c r="B183" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C183" s="2">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A184" s="2">
+        <v>91791</v>
+      </c>
+      <c r="B184" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C184" s="2">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A185" s="2">
+        <v>92293</v>
+      </c>
+      <c r="B185" s="2">
+        <v>20.04</v>
+      </c>
+      <c r="C185" s="2">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A186" s="2">
+        <v>92793</v>
+      </c>
+      <c r="B186" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C186" s="2">
+        <v>23.07</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A187" s="2">
+        <v>93295</v>
+      </c>
+      <c r="B187" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C187" s="2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A188" s="2">
+        <v>93797</v>
+      </c>
+      <c r="B188" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C188" s="2">
+        <v>22.87</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A189" s="2">
+        <v>94299</v>
+      </c>
+      <c r="B189" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C189" s="2">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A190" s="2">
+        <v>94800</v>
+      </c>
+      <c r="B190" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C190" s="2">
+        <v>23.07</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A191" s="2">
+        <v>95302</v>
+      </c>
+      <c r="B191" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C191" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A192" s="2">
+        <v>95803</v>
+      </c>
+      <c r="B192" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C192" s="2">
+        <v>22.48</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A193" s="2">
+        <v>96305</v>
+      </c>
+      <c r="B193" s="2">
+        <v>16.62</v>
+      </c>
+      <c r="C193" s="2">
+        <v>22.39</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A194" s="2">
+        <v>96806</v>
+      </c>
+      <c r="B194" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C194" s="2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A195" s="2">
+        <v>97308</v>
+      </c>
+      <c r="B195" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C195" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A196" s="2">
+        <v>97810</v>
+      </c>
+      <c r="B196" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C196" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A197" s="2">
+        <v>98311</v>
+      </c>
+      <c r="B197" s="2">
+        <v>16.62</v>
+      </c>
+      <c r="C197" s="2">
+        <v>22.19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A198" s="2">
+        <v>98812</v>
+      </c>
+      <c r="B198" s="2">
+        <v>16.13</v>
+      </c>
+      <c r="C198" s="2">
+        <v>22.39</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A199" s="2">
+        <v>99314</v>
+      </c>
+      <c r="B199" s="2">
+        <v>16.62</v>
+      </c>
+      <c r="C199" s="2">
+        <v>22.48</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A200" s="2">
+        <v>99816</v>
+      </c>
+      <c r="B200" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C200" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="2">
+        <v>100318</v>
+      </c>
+      <c r="B201" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C201" s="2">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A202" s="2">
+        <v>100818</v>
+      </c>
+      <c r="B202" s="2">
+        <v>16.62</v>
+      </c>
+      <c r="C202" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A203" s="2">
+        <v>101320</v>
+      </c>
+      <c r="B203" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C203" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A204" s="2">
+        <v>101822</v>
+      </c>
+      <c r="B204" s="2">
+        <v>16.62</v>
+      </c>
+      <c r="C204" s="2">
+        <v>23.17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A205" s="2">
+        <v>102324</v>
+      </c>
+      <c r="B205" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C205" s="2">
+        <v>22.29</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A206" s="2">
+        <v>102825</v>
+      </c>
+      <c r="B206" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C206" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A207" s="2">
+        <v>103327</v>
+      </c>
+      <c r="B207" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C207" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A208" s="2">
+        <v>103828</v>
+      </c>
+      <c r="B208" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C208" s="2">
+        <v>23.07</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A209" s="2">
+        <v>104330</v>
+      </c>
+      <c r="B209" s="2">
+        <v>15.15</v>
+      </c>
+      <c r="C209" s="2">
+        <v>23.26</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A210" s="2">
+        <v>104832</v>
+      </c>
+      <c r="B210" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C210" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A211" s="2">
+        <v>105333</v>
+      </c>
+      <c r="B211" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C211" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A212" s="2">
+        <v>105835</v>
+      </c>
+      <c r="B212" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C212" s="2">
+        <v>23.66</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A213" s="2">
+        <v>106337</v>
+      </c>
+      <c r="B213" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C213" s="2">
+        <v>22.09</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="2">
+        <v>106839</v>
+      </c>
+      <c r="B214" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C214" s="2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A215" s="2">
+        <v>107339</v>
+      </c>
+      <c r="B215" s="2">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="C215" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A216" s="2">
+        <v>107841</v>
+      </c>
+      <c r="B216" s="2">
+        <v>16.62</v>
+      </c>
+      <c r="C216" s="2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A217" s="2">
+        <v>108343</v>
+      </c>
+      <c r="B217" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C217" s="2">
+        <v>22.97</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A218" s="2">
+        <v>108845</v>
+      </c>
+      <c r="B218" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C218" s="2">
+        <v>23.36</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A219" s="2">
+        <v>109346</v>
+      </c>
+      <c r="B219" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C219" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A220" s="2">
+        <v>109848</v>
+      </c>
+      <c r="B220" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C220" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A221" s="2">
+        <v>110350</v>
+      </c>
+      <c r="B221" s="2">
+        <v>16.62</v>
+      </c>
+      <c r="C221" s="2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="2">
+        <v>110851</v>
+      </c>
+      <c r="B222" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C222" s="2">
+        <v>22.39</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="2">
+        <v>111352</v>
+      </c>
+      <c r="B223" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C223" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A224" s="2">
+        <v>111854</v>
+      </c>
+      <c r="B224" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C224" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A225" s="2">
+        <v>112356</v>
+      </c>
+      <c r="B225" s="2">
+        <v>19.059999999999999</v>
+      </c>
+      <c r="C225" s="2">
+        <v>22.97</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A226" s="2">
+        <v>112858</v>
+      </c>
+      <c r="B226" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C226" s="2">
+        <v>23.56</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A227" s="2">
+        <v>113359</v>
+      </c>
+      <c r="B227" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C227" s="2">
+        <v>21.51</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A228" s="2">
+        <v>113860</v>
+      </c>
+      <c r="B228" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C228" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A229" s="2">
+        <v>114362</v>
+      </c>
+      <c r="B229" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C229" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230" s="2">
+        <v>114864</v>
+      </c>
+      <c r="B230" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C230" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A231" s="2">
+        <v>115365</v>
+      </c>
+      <c r="B231" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C231" s="2">
+        <v>20.82</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A232" s="2">
+        <v>115867</v>
+      </c>
+      <c r="B232" s="2">
+        <v>17.11</v>
+      </c>
+      <c r="C232" s="2">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A233" s="2">
+        <v>116369</v>
+      </c>
+      <c r="B233" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C233" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A234" s="2">
+        <v>116871</v>
+      </c>
+      <c r="B234" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C234" s="2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A235" s="2">
+        <v>117371</v>
+      </c>
+      <c r="B235" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C235" s="2">
+        <v>22.19</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A236" s="2">
+        <v>117873</v>
+      </c>
+      <c r="B236" s="2">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="C236" s="2">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A237" s="2">
+        <v>118375</v>
+      </c>
+      <c r="B237" s="2">
+        <v>18.57</v>
+      </c>
+      <c r="C237" s="2">
+        <v>22.68</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>